--- a/data/final_interview_schedule.xlsx
+++ b/data/final_interview_schedule.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,44 +453,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Pooja Mehta</t>
+          <t>Anita Verma</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>frontend developer</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>30-01-2026 10:30 AM</t>
+          <t>09-03-2026 07:50 PM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://meet.google.com/aui-wdus-zqy</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Rahul Sharma</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>27-01-2026 07:23 PM</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>https://meet.google.com/qai-tymw-ucg</t>
+          <t>https://meet.google.com/gbo-dknb-xia</t>
         </is>
       </c>
     </row>

--- a/data/final_interview_schedule.xlsx
+++ b/data/final_interview_schedule.xlsx
@@ -463,12 +463,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>09-03-2026 07:50 PM</t>
+          <t>09-03-2026 07:00 PM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://meet.google.com/gbo-dknb-xia</t>
+          <t>https://meet.google.com/ohc-aqpp-qgj</t>
         </is>
       </c>
     </row>
